--- a/AtchisonRegime/Outputs/Euro/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Euro/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
@@ -1176,13 +1176,13 @@
         <v>45260</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3192256749734665</v>
+        <v>0.3136059541525436</v>
       </c>
     </row>
   </sheetData>
